--- a/飞书表格.xlsx
+++ b/飞书表格.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="指标配置表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日数据表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周汇总表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题跟踪表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="指标配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="每日数据表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="周汇总表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="问题跟踪表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="122211" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -95094,7 +95094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95115,20 +95115,25 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>行动</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>计划关闭日期</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>实际关闭日期</t>
         </is>
